--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260819.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260819.xlsx
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>41,370,000</t>
+          <t>7,990,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>7,990,000</t>
+          <t>13,510,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>13,510,000</t>
+          <t>41,370,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
